--- a/artfynd/A 13012-2022 artfynd.xlsx
+++ b/artfynd/A 13012-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13012-2022 artfynd.xlsx
+++ b/artfynd/A 13012-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2456987</v>
+        <v>449907</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>1666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brömsbodakärret, Srm</t>
+          <t>Bromsbodakärret, sumpviol 450 m VSV om Bromsboda, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616482.6373294014</v>
+        <v>616425</v>
       </c>
       <c r="R2" t="n">
-        <v>6571512.7714155</v>
+        <v>6571717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,24 @@
           <t>Åker</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>D-Str-0124</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1977-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1977-06-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hotas av skogsbruk, En rad nederbördsfattiga år har missgynnat arten. Avverkning. 2 bestånd ett stort och ett litet m. ett avstånd från varandra på 50 m. Båda bestånden i bäckens absoluta närhet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,33 +778,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Utglesat skogskärr. Floran relativt artrik</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Flodin</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Flodin, Göran Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>D-län Floraväktarna, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>453007</v>
       </c>
       <c r="B3" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616511.7343145724</v>
+        <v>616512</v>
       </c>
       <c r="R3" t="n">
-        <v>6571583.232052383</v>
+        <v>6571583</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,19 +875,9 @@
           <t>1998-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,15 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53733997</v>
+        <v>455688</v>
       </c>
       <c r="B4" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,12 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -983,20 +957,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bromsbodakärret, Berga säteri, Srm</t>
+          <t>Brömsbodakärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616446.6233665086</v>
+        <v>616483</v>
       </c>
       <c r="R4" t="n">
-        <v>6571584.304295918</v>
+        <v>6571513</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,27 +993,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-05-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-06-11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>125 blommande ex</t>
+          <t>Enstaka exemplar överblommade.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,16 +1014,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Per Flodin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Per Flodin, Göran Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1070,12 +1038,7 @@
         <v>455689</v>
       </c>
       <c r="B5" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616451.5912647154</v>
+        <v>616452</v>
       </c>
       <c r="R5" t="n">
-        <v>6571572.691525317</v>
+        <v>6571573</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,19 +1108,9 @@
           <t>2005-06-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1194,15 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>455688</v>
+        <v>53733997</v>
       </c>
       <c r="B6" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1177,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1237,19 +1190,20 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brömsbodakärret, Srm</t>
+          <t>Bromsbodakärret, Berga säteri, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616482.6373294014</v>
+        <v>616447</v>
       </c>
       <c r="R6" t="n">
-        <v>6571512.7714155</v>
+        <v>6571584</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,27 +1227,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka exemplar överblommade.</t>
+          <t>125 blommande ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,21 +1248,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Flodin</t>
+          <t>Bernt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Flodin, Göran Andersson</t>
+          <t>Bernt Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1328,12 +1267,7 @@
         <v>71444730</v>
       </c>
       <c r="B7" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616435.9042736489</v>
+        <v>616436</v>
       </c>
       <c r="R7" t="n">
-        <v>6571633.081732658</v>
+        <v>6571633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,19 +1335,9 @@
           <t>2018-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-05-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1443,64 +1367,61 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Strid, Nicklas Johansson</t>
+          <t>Nicklas Johansson, Thomas Strid</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>85710674</v>
+        <v>78624994</v>
       </c>
       <c r="B8" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2412</v>
+        <v>1666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bromsbodakärret, Berga säteri, Srm</t>
+          <t>Strängnäs kommun, Södermanlands län, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616446.6233665086</v>
+        <v>616434</v>
       </c>
       <c r="R8" t="n">
-        <v>6571584.304295918</v>
+        <v>6571719</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,22 +1445,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-05-23</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-05-23</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,85 +1469,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Jukka Väyrynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Jukka Väyrynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94141826</v>
+        <v>93577623</v>
       </c>
       <c r="B9" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100088</v>
+        <v>1666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bromsbodakärret, Berga säteri, Srm</t>
+          <t>Bromsbodakärret, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616446.6233665086</v>
+        <v>616430</v>
       </c>
       <c r="R9" t="n">
-        <v>6571584.304295918</v>
+        <v>6571720</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,22 +1556,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor. Växter strax höger om boken.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,19 +1585,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1696,12 +1606,7 @@
         <v>97040510</v>
       </c>
       <c r="B10" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616481.1432140296</v>
+        <v>616481</v>
       </c>
       <c r="R10" t="n">
-        <v>6571528.071608325</v>
+        <v>6571528</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1774,19 +1679,9 @@
           <t>2005-06-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2005-06-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,12 +1712,7 @@
         <v>100310237</v>
       </c>
       <c r="B11" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616442.2355446173</v>
+        <v>616442</v>
       </c>
       <c r="R11" t="n">
-        <v>6571627.137619475</v>
+        <v>6571627</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1887,19 +1777,9 @@
           <t>1980-06-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1980-08-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1934,12 +1814,7 @@
         <v>109103658</v>
       </c>
       <c r="B12" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616439.4306036278</v>
+        <v>616439</v>
       </c>
       <c r="R12" t="n">
-        <v>6571668.484450616</v>
+        <v>6571668</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2016,19 +1891,9 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2061,47 +1926,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110641975</v>
+        <v>85710674</v>
       </c>
       <c r="B13" t="n">
-        <v>56289</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100001</v>
+        <v>2412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2109,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>616446.6233665086</v>
+        <v>616447</v>
       </c>
       <c r="R13" t="n">
-        <v>6571584.304295918</v>
+        <v>6571584</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2139,27 +1995,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En duvhök lämnade boet, troligen en årsunge. Sitter nu och lockar ca 100m bort.</t>
+          <t>2020-05-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,6 +2009,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2183,6 +2025,545 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110641975</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bromsbodakärret, Berga säteri, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>616447</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6571584</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En duvhök lämnade boet, troligen en årsunge. Sitter nu och lockar ca 100m bort.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94141826</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bromsbodakärret, Berga säteri, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>616447</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6571584</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>99625777</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bromsbodakärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>616480</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6571515</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-03-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-03-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2456987</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brömsbodakärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>616483</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6571513</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2005-06-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2005-06-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Flodin, Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>78634403</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strängnäs kommun, Södermanlands län, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>616434</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6571719</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-06-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-06-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jukka Väyrynen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jukka Väyrynen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13012-2022 artfynd.xlsx
+++ b/artfynd/A 13012-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/449907</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/453007</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/455688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/455689</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53733997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1371,6 +1401,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71444730</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78624994</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93577623</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97040510</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1808,6 +1858,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100310237</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109103658</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2025,6 +2085,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85710674</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2135,6 +2200,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110641975</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2246,6 +2316,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94141826</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2351,6 +2426,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99625777</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2462,6 +2542,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2456987</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,8 +2649,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78634403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>